--- a/Result/profitability/3044.xlsx
+++ b/Result/profitability/3044.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.96</v>
       </c>
       <c r="M2" t="n">
-        <v>4.46</v>
+        <v>4.83375</v>
       </c>
       <c r="N2" t="n">
-        <v>24.5625</v>
+        <v>25.3875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.65</v>
       </c>
       <c r="M3" t="n">
-        <v>4.11375</v>
+        <v>4.510000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>23.98625</v>
+        <v>24.71375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>1.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.82125</v>
+        <v>4.1875</v>
       </c>
       <c r="N4" t="n">
-        <v>23.625</v>
+        <v>24.265</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>3.350000000000001</v>
+        <v>3.695</v>
       </c>
       <c r="N5" t="n">
-        <v>22.32875</v>
+        <v>22.81375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.52</v>
       </c>
       <c r="M6" t="n">
-        <v>2.83375</v>
+        <v>3.0575</v>
       </c>
       <c r="N6" t="n">
-        <v>20.7475</v>
+        <v>21.16375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>2.29125</v>
+        <v>2.63</v>
       </c>
       <c r="N7" t="n">
-        <v>19.68125</v>
+        <v>20.25875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.46</v>
       </c>
       <c r="M8" t="n">
-        <v>2.01125</v>
+        <v>2.23625</v>
       </c>
       <c r="N8" t="n">
-        <v>19.3975</v>
+        <v>19.845</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>24857</v>
+      </c>
+      <c r="D75" t="n">
+        <v>17378</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7479</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5585</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.47%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>96</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5681</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3896</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5.14125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.97125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.320855614973262</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.579999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1350433798566577</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5935483870967742</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.879999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1480351011064478</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
